--- a/Assets/Project1026/06.Datas/Excel/ExcelData.xlsx
+++ b/Assets/Project1026/06.Datas/Excel/ExcelData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\Project1026\Assets\Project1026\06.Datas\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D783CCAE-8239-48EC-9FC9-7DE060FF9486}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17C6299C-C62E-45D7-948F-C539FBE18B34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PlayerStat" sheetId="1" r:id="rId1"/>
@@ -596,7 +596,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2">
-        <v>5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="24" customHeight="1">
@@ -612,7 +612,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="2">
-        <v>7</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="24" customHeight="1">
@@ -628,7 +628,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="24" customHeight="1">
@@ -636,7 +636,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="24" customHeight="1">
@@ -644,7 +644,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="24" customHeight="1">
@@ -652,7 +652,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="2">
-        <v>8</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="24" customHeight="1">
@@ -1133,5 +1133,6 @@
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>